--- a/backend/InternLink/InternLink.API/Templates/Lich huong dan TTTN-C23-Cuong.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/Lich huong dan TTTN-C23-Cuong.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312E83DC-AC46-4499-8A7B-81A65706FDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811E856F-49B8-4B1F-951C-E547C3B4A485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,10 +138,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-  </numFmts>
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -218,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -253,19 +249,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -290,17 +273,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -435,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -467,12 +439,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -483,15 +449,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -504,15 +461,30 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -528,71 +500,41 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -899,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" customWidth="1"/>
@@ -908,11 +850,11 @@
     <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.33203125" style="22" customWidth="1"/>
+    <col min="11" max="11" width="22.33203125" style="17" customWidth="1"/>
     <col min="12" max="12" width="8" style="1" hidden="1" customWidth="1"/>
     <col min="13" max="249" width="8.88671875" style="1"/>
     <col min="250" max="250" width="5.6640625" style="1" customWidth="1"/>
@@ -1801,41 +1743,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21.9" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" ht="21.9" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="21.9" customHeight="1">
@@ -1854,20 +1796,20 @@
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="21.9" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="21.9" customHeight="1">
@@ -1888,358 +1830,223 @@
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" customFormat="1" ht="21.9" customHeight="1">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="21"/>
+      <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:13" s="8" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="35" t="s">
+      <c r="H7" s="40"/>
+      <c r="I7" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
       <c r="L7" s="6"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="21.9" customHeight="1" thickBot="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="39" t="s">
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="20" t="s">
         <v>6</v>
       </c>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A9" s="52" t="s">
+    <row r="9" spans="1:13" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="53" t="s">
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="28" t="s">
         <v>31</v>
       </c>
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A10" s="54"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="24"/>
+    <row r="10" spans="1:13" ht="21.9" customHeight="1" thickBot="1">
+      <c r="A10" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25">
+        <f>SUM(D9:D9)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="43"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A11" s="54"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="11"/>
+    <row r="11" spans="1:13">
+      <c r="H11" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1">
-      <c r="A12" s="54"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="11"/>
+    <row r="12" spans="1:13">
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:13" ht="31.5" customHeight="1">
-      <c r="A13" s="54"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="11"/>
+    <row r="13" spans="1:13" s="8" customFormat="1" ht="31.5" customHeight="1">
+      <c r="A13" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="G13" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="30"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1">
-      <c r="A14" s="54"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="12"/>
+    <row r="14" spans="1:13">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A15" s="54"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="55"/>
+    <row r="15" spans="1:13" s="8" customFormat="1">
+      <c r="I15" s="12"/>
+      <c r="K15" s="18"/>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A16" s="54"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="55"/>
+    <row r="16" spans="1:13" s="8" customFormat="1">
+      <c r="I16" s="12"/>
+      <c r="K16" s="18"/>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="1:12" ht="30" customHeight="1">
-      <c r="A17" s="54"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="12"/>
+    <row r="17" spans="1:12" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="D17" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="30"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="30"/>
     </row>
-    <row r="18" spans="1:12" ht="33" customHeight="1" thickBot="1">
-      <c r="A18" s="54"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="12"/>
+    <row r="18" spans="1:12" s="8" customFormat="1">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" ht="21.9" customHeight="1" thickBot="1">
-      <c r="A19" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="47">
-        <f>SUM(D9:D18)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="48"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="13"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="H20" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="15"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="15"/>
-    </row>
-    <row r="22" spans="1:12" s="8" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="34"/>
-      <c r="G22" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="28"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-    </row>
-    <row r="24" spans="1:12" s="8" customFormat="1">
-      <c r="I24" s="14"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" spans="1:12" s="8" customFormat="1">
-      <c r="I25" s="14"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" spans="1:12" s="8" customFormat="1" ht="15.75" customHeight="1">
-      <c r="D26" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" s="28"/>
-    </row>
-    <row r="27" spans="1:12" s="8" customFormat="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="1"/>
-    </row>
-    <row r="28" spans="1:12" s="8" customFormat="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="1"/>
+    <row r="19" spans="1:12" s="8" customFormat="1">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="20">
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E15:J15"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H11:K11"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="E18:J18"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="A2:F2"/>
